--- a/data/trans_dic/P23_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,24; 40,95</t>
+          <t>31,7; 40,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 34,89</t>
+          <t>26,36; 34,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,51; 38,64</t>
+          <t>29,57; 38,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,42; 31,14</t>
+          <t>16,53; 30,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,36; 38,48</t>
+          <t>29,07; 37,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 38,25</t>
+          <t>28,32; 37,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,62; 30,99</t>
+          <t>22,6; 31,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,55; 26,06</t>
+          <t>14,59; 26,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,94; 38,01</t>
+          <t>31,95; 37,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,32; 34,76</t>
+          <t>28,54; 34,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,48; 34,07</t>
+          <t>27,19; 33,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,38; 26,93</t>
+          <t>16,94; 27,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,83; 53,21</t>
+          <t>45,55; 53,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,27; 47,65</t>
+          <t>39,77; 47,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,02; 48,34</t>
+          <t>40,31; 48,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,75; 40,81</t>
+          <t>29,68; 40,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,37; 38,83</t>
+          <t>31,24; 38,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,67; 44,05</t>
+          <t>36,2; 44,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,58; 41,49</t>
+          <t>33,52; 41,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,12; 27,93</t>
+          <t>13,56; 27,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,08; 45,64</t>
+          <t>39,97; 45,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 45,03</t>
+          <t>39,28; 44,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,18; 43,96</t>
+          <t>38,12; 43,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,52; 32,11</t>
+          <t>21,62; 32,23</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,23; 56,22</t>
+          <t>48,14; 56,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,14; 49,48</t>
+          <t>42,06; 49,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,18; 43,99</t>
+          <t>36,07; 43,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,62; 31,55</t>
+          <t>24,14; 31,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,57; 40,98</t>
+          <t>33,34; 41,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,77; 37,93</t>
+          <t>30,36; 38,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,07; 37,05</t>
+          <t>29,97; 37,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,09; 28,29</t>
+          <t>22,17; 28,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,68; 47,03</t>
+          <t>41,66; 46,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,34; 42,63</t>
+          <t>37,28; 42,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,06; 39,6</t>
+          <t>34,04; 39,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,96; 28,86</t>
+          <t>23,89; 28,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,64; 48,6</t>
+          <t>39,49; 48,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,1; 50,11</t>
+          <t>40,99; 49,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,19; 47,2</t>
+          <t>38,82; 47,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 30,07</t>
+          <t>9,49; 30,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 31,46</t>
+          <t>23,54; 31,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,99; 43,3</t>
+          <t>34,94; 43,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,78; 39,59</t>
+          <t>31,74; 39,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,06; 25,55</t>
+          <t>19,06; 25,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,85; 39,06</t>
+          <t>32,89; 38,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,11; 45,19</t>
+          <t>39,07; 44,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,66; 42,58</t>
+          <t>36,54; 42,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 26,24</t>
+          <t>12,82; 26,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,3; 38,14</t>
+          <t>29,08; 38,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,64; 41,32</t>
+          <t>31,21; 40,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,37; 35,5</t>
+          <t>26,25; 35,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,32; 34,65</t>
+          <t>27,41; 34,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 15,21</t>
+          <t>8,81; 15,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 19,09</t>
+          <t>11,92; 19,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 27,46</t>
+          <t>19,21; 26,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,54; 24,78</t>
+          <t>19,61; 25,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,16; 25,35</t>
+          <t>19,3; 25,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 28,62</t>
+          <t>22,19; 28,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,87; 30,05</t>
+          <t>23,97; 29,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,64; 29,19</t>
+          <t>24,49; 29,04</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 22,79</t>
+          <t>13,99; 22,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,12; 21,62</t>
+          <t>12,66; 22,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 21,7</t>
+          <t>13,13; 22,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,55; 22,4</t>
+          <t>15,46; 22,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,12</t>
+          <t>0,83; 3,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,37</t>
+          <t>3,2; 8,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 11,49</t>
+          <t>5,19; 11,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 12,95</t>
+          <t>3,43; 13,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,82</t>
+          <t>7,56; 11,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 13,35</t>
+          <t>8,14; 13,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,94</t>
+          <t>10,14; 15,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,81; 15,86</t>
+          <t>6,32; 15,79</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 15,65</t>
+          <t>7,34; 15,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,06; 15,5</t>
+          <t>7,08; 15,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,9</t>
+          <t>6,65; 12,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,57</t>
+          <t>4,75; 9,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,2</t>
+          <t>0,33; 3,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,89</t>
+          <t>0,26; 3,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,07</t>
+          <t>0,69; 4,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,43</t>
+          <t>0,78; 2,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,08</t>
+          <t>3,33; 6,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,12</t>
+          <t>3,36; 6,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,67</t>
+          <t>3,41; 6,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,84</t>
+          <t>2,62; 4,84</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,0; 41,57</t>
+          <t>38,25; 41,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,21; 38,77</t>
+          <t>35,12; 38,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,99; 36,39</t>
+          <t>32,98; 36,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,25; 26,8</t>
+          <t>19,06; 26,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,23; 26,21</t>
+          <t>23,11; 25,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,37; 28,5</t>
+          <t>25,46; 28,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,6; 27,56</t>
+          <t>24,57; 27,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,36; 19,5</t>
+          <t>14,79; 19,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,89; 33,31</t>
+          <t>30,93; 33,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,6; 32,99</t>
+          <t>30,69; 32,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,37</t>
+          <t>29,08; 31,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,1; 22,57</t>
+          <t>17,91; 22,56</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>158961; 201892</t>
+          <t>156271; 199676</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>117867; 158445</t>
+          <t>119696; 158295</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123790; 162101</t>
+          <t>124021; 162345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65669; 124562</t>
+          <t>66135; 123357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>137242; 179899</t>
+          <t>135897; 175500</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>123929; 164203</t>
+          <t>121563; 159722</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89523; 122649</t>
+          <t>89449; 124019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45191; 80968</t>
+          <t>45337; 82045</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>306823; 365086</t>
+          <t>306871; 364666</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>250155; 307097</t>
+          <t>252132; 307256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>224044; 277723</t>
+          <t>221671; 275568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>123500; 191385</t>
+          <t>120401; 195586</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>337101; 391362</t>
+          <t>335011; 391410</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>276674; 327411</t>
+          <t>273260; 328952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236312; 285444</t>
+          <t>238045; 288415</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121781; 172866</t>
+          <t>125692; 173285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>196209; 242893</t>
+          <t>195432; 240268</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>223768; 268793</t>
+          <t>220919; 269779</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>189244; 233821</t>
+          <t>188908; 234719</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72213; 142867</t>
+          <t>69341; 142967</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>545432; 621129</t>
+          <t>544038; 621101</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511346; 584180</t>
+          <t>509660; 582552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>440642; 507331</t>
+          <t>439919; 505781</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>201184; 300261</t>
+          <t>202145; 301354</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>308012; 359030</t>
+          <t>307474; 357688</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>286871; 336858</t>
+          <t>286354; 338159</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>241681; 293841</t>
+          <t>240988; 291463</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126658; 169151</t>
+          <t>129432; 171049</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>231565; 282635</t>
+          <t>229990; 286067</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>218414; 269257</t>
+          <t>215494; 269927</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>198589; 244723</t>
+          <t>197920; 245906</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>119834; 153475</t>
+          <t>120260; 154092</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>553652; 624690</t>
+          <t>553476; 623502</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>519275; 592873</t>
+          <t>518472; 593966</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>452492; 526036</t>
+          <t>452222; 524396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>258470; 311262</t>
+          <t>257721; 311825</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>205801; 252297</t>
+          <t>204989; 253173</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252629; 308003</t>
+          <t>251918; 305007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>253205; 304927</t>
+          <t>250782; 304513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79932; 266663</t>
+          <t>84197; 269133</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>121958; 162220</t>
+          <t>121383; 162251</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>215624; 266833</t>
+          <t>215303; 267130</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>205606; 256156</t>
+          <t>205357; 254014</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>135644; 181768</t>
+          <t>135634; 183129</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>339881; 404180</t>
+          <t>340376; 399970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>481340; 556150</t>
+          <t>480821; 552838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>474020; 550508</t>
+          <t>472457; 544996</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>193424; 419401</t>
+          <t>204890; 422474</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>109441; 147496</t>
+          <t>112451; 147281</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>135866; 177455</t>
+          <t>134040; 175997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126011; 169646</t>
+          <t>125451; 168060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153041; 194118</t>
+          <t>153573; 195400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35857; 61454</t>
+          <t>35575; 62900</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52747; 85471</t>
+          <t>53366; 85060</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95907; 136149</t>
+          <t>95243; 133819</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>107073; 135744</t>
+          <t>107426; 137912</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>151494; 200470</t>
+          <t>152635; 199747</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>197585; 251066</t>
+          <t>194661; 252713</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232382; 292545</t>
+          <t>233352; 289122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>273028; 323486</t>
+          <t>271396; 321799</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41938; 66669</t>
+          <t>40946; 66732</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37554; 66987</t>
+          <t>39213; 68496</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45592; 72535</t>
+          <t>43907; 74340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57240; 82457</t>
+          <t>56929; 81252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2826; 14123</t>
+          <t>2833; 13351</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11513; 29630</t>
+          <t>11317; 30472</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20451; 43407</t>
+          <t>19593; 41574</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19774; 78799</t>
+          <t>20846; 79770</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47755; 75126</t>
+          <t>48053; 76143</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54166; 88616</t>
+          <t>54010; 90789</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71407; 106354</t>
+          <t>72234; 110461</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>66530; 154890</t>
+          <t>61668; 154196</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15017; 32851</t>
+          <t>15410; 32477</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17630; 38738</t>
+          <t>17695; 38070</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16386; 33050</t>
+          <t>17042; 33185</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12443; 27060</t>
+          <t>13438; 26929</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1130; 10701</t>
+          <t>1115; 11607</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1009; 11236</t>
+          <t>1009; 12889</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2770; 16241</t>
+          <t>2768; 16517</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3290; 10352</t>
+          <t>3323; 10957</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18368; 38526</t>
+          <t>18099; 37871</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21035; 45472</t>
+          <t>21474; 44440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21137; 43701</t>
+          <t>22306; 44679</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18777; 34277</t>
+          <t>18576; 34325</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1244842; 1361477</t>
+          <t>1252736; 1365380</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1206177; 1328041</t>
+          <t>1203028; 1319774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1119083; 1234664</t>
+          <t>1118666; 1233119</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>665502; 926490</t>
+          <t>659122; 919495</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>785050; 885840</t>
+          <t>781070; 876985</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>902400; 1013655</t>
+          <t>905512; 1012153</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>870508; 975209</t>
+          <t>869521; 974405</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>525297; 713537</t>
+          <t>541235; 718797</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2055957; 2216426</t>
+          <t>2058038; 2217789</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2136501; 2303716</t>
+          <t>2142650; 2302854</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2015020; 2174439</t>
+          <t>2015671; 2174376</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1287875; 1605712</t>
+          <t>1274431; 1605487</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,7; 40,5</t>
+          <t>31,86; 40,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,36; 34,86</t>
+          <t>25,6; 34,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,57; 38,7</t>
+          <t>29,55; 38,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,53; 30,84</t>
+          <t>16,36; 30,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,07; 37,54</t>
+          <t>29,3; 37,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,32; 37,21</t>
+          <t>28,4; 37,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,6; 31,34</t>
+          <t>22,4; 31,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,59; 26,41</t>
+          <t>14,02; 25,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,95; 37,97</t>
+          <t>31,63; 38,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,78</t>
+          <t>28,62; 34,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,19; 33,8</t>
+          <t>27,29; 33,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 27,52</t>
+          <t>16,94; 25,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,55; 53,22</t>
+          <t>45,34; 52,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,77; 47,88</t>
+          <t>40,13; 47,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,31; 48,84</t>
+          <t>39,77; 48,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,68; 40,91</t>
+          <t>29,25; 40,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,24; 38,41</t>
+          <t>30,98; 38,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,2; 44,21</t>
+          <t>36,23; 44,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,52; 41,65</t>
+          <t>33,92; 42,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,56; 27,95</t>
+          <t>20,22; 28,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,97; 45,64</t>
+          <t>39,86; 45,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39,28; 44,9</t>
+          <t>39,23; 44,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,12; 43,83</t>
+          <t>38,13; 43,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,62; 32,23</t>
+          <t>25,66; 32,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,14; 56,01</t>
+          <t>48,01; 56,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,06; 49,67</t>
+          <t>41,95; 49,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 43,63</t>
+          <t>36,28; 43,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,14; 31,9</t>
+          <t>23,46; 30,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,34; 41,47</t>
+          <t>33,5; 40,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,36; 38,03</t>
+          <t>30,38; 37,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,97; 37,23</t>
+          <t>29,87; 37,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,17; 28,41</t>
+          <t>20,58; 26,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,66; 46,94</t>
+          <t>41,52; 47,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 42,71</t>
+          <t>37,48; 42,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,04; 39,47</t>
+          <t>33,92; 39,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,89; 28,91</t>
+          <t>22,97; 27,76</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,49; 48,77</t>
+          <t>39,61; 48,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,99; 49,63</t>
+          <t>41,18; 49,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 47,13</t>
+          <t>38,66; 47,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 30,35</t>
+          <t>24,43; 31,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,54; 31,47</t>
+          <t>23,75; 31,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,94; 43,35</t>
+          <t>34,45; 42,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,74; 39,26</t>
+          <t>31,72; 39,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,06; 25,74</t>
+          <t>21,52; 26,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,89; 38,65</t>
+          <t>32,8; 38,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,07; 44,92</t>
+          <t>39,05; 44,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36,54; 42,15</t>
+          <t>36,5; 42,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 26,43</t>
+          <t>23,63; 27,86</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,08; 38,09</t>
+          <t>28,3; 37,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,21; 40,98</t>
+          <t>31,66; 41,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,25; 35,17</t>
+          <t>26,19; 35,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,41; 34,88</t>
+          <t>27,54; 35,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 15,57</t>
+          <t>8,38; 15,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 19,0</t>
+          <t>11,88; 19,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,21; 26,99</t>
+          <t>19,06; 26,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,61; 25,17</t>
+          <t>19,8; 24,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,3; 25,26</t>
+          <t>19,42; 25,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,19; 28,81</t>
+          <t>22,31; 28,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,97; 29,69</t>
+          <t>23,8; 29,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,49; 29,04</t>
+          <t>24,37; 29,13</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,99; 22,81</t>
+          <t>14,17; 22,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,66; 22,11</t>
+          <t>12,44; 21,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,13; 22,24</t>
+          <t>13,22; 21,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,46; 22,07</t>
+          <t>15,37; 22,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,89</t>
+          <t>0,82; 3,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,61</t>
+          <t>3,21; 8,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,01</t>
+          <t>5,51; 10,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 13,11</t>
+          <t>10,3; 15,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,98</t>
+          <t>7,47; 12,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,68</t>
+          <t>8,44; 13,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,51</t>
+          <t>10,16; 15,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,32; 15,79</t>
+          <t>13,55; 17,38</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,47</t>
+          <t>6,95; 15,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 15,24</t>
+          <t>7,32; 15,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 12,96</t>
+          <t>6,56; 13,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,52</t>
+          <t>4,32; 9,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,48</t>
+          <t>0,34; 3,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,31</t>
+          <t>0,26; 3,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,14</t>
+          <t>0,68; 4,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,57</t>
+          <t>0,78; 2,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,96</t>
+          <t>3,45; 7,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,96</t>
+          <t>3,22; 7,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,82</t>
+          <t>3,43; 6,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,84</t>
+          <t>2,52; 4,76</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,25; 41,68</t>
+          <t>38,16; 41,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,12; 38,53</t>
+          <t>35,25; 38,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,98; 36,35</t>
+          <t>33,22; 36,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,06; 26,59</t>
+          <t>24,02; 27,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,11; 25,95</t>
+          <t>23,14; 26,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,46; 28,46</t>
+          <t>25,35; 28,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,57; 27,53</t>
+          <t>24,58; 27,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,65</t>
+          <t>17,85; 20,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,93; 33,33</t>
+          <t>30,98; 33,19</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,69; 32,98</t>
+          <t>30,66; 33,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,37</t>
+          <t>29,14; 31,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,91; 22,56</t>
+          <t>21,06; 23,18</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91625</t>
+          <t>93153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>68600</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>153298</t>
+          <t>161754</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>156271; 199676</t>
+          <t>157065; 201344</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>119696; 158295</t>
+          <t>116265; 157058</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>124021; 162345</t>
+          <t>123939; 161891</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66135; 123357</t>
+          <t>66707; 123126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>135897; 175500</t>
+          <t>136996; 175946</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>121563; 159722</t>
+          <t>121891; 160597</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89449; 124019</t>
+          <t>88657; 123711</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45337; 82045</t>
+          <t>50465; 93511</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>306871; 364666</t>
+          <t>303853; 365447</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>252132; 307256</t>
+          <t>252790; 308436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>221671; 275568</t>
+          <t>222468; 276471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>120401; 195586</t>
+          <t>130110; 197039</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147029</t>
+          <t>161617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>114930</t>
+          <t>122038</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>261959</t>
+          <t>283654</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>335011; 391410</t>
+          <t>333473; 388370</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273260; 328952</t>
+          <t>275758; 328139</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238045; 288415</t>
+          <t>234816; 284272</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125692; 173285</t>
+          <t>139470; 191350</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>195432; 240268</t>
+          <t>193774; 243588</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>220919; 269779</t>
+          <t>221066; 270339</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>188908; 234719</t>
+          <t>191132; 237623</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69341; 142967</t>
+          <t>101318; 143451</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>544038; 621101</t>
+          <t>542433; 617650</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>509660; 582552</t>
+          <t>508964; 579886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>439919; 505781</t>
+          <t>440089; 505162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>202145; 301354</t>
+          <t>250915; 315727</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149647</t>
+          <t>168348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>135854</t>
+          <t>146458</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>285502</t>
+          <t>314806</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>307474; 357688</t>
+          <t>306650; 362088</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>286354; 338159</t>
+          <t>285588; 337111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>240988; 291463</t>
+          <t>242329; 293195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129432; 171049</t>
+          <t>145389; 191965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>229990; 286067</t>
+          <t>231056; 281802</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>215494; 269927</t>
+          <t>215636; 268170</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>197920; 245906</t>
+          <t>197257; 245724</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>120260; 154092</t>
+          <t>128040; 163810</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>553476; 623502</t>
+          <t>551574; 624465</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>518472; 593966</t>
+          <t>521181; 593353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>452222; 524396</t>
+          <t>450557; 523866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>257721; 311825</t>
+          <t>285302; 344754</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184758</t>
+          <t>195321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>162735</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>347493</t>
+          <t>369762</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>204989; 253173</t>
+          <t>205647; 251252</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>251918; 305007</t>
+          <t>253112; 304378</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>250782; 304513</t>
+          <t>249750; 305086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84197; 269133</t>
+          <t>170871; 220042</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>121383; 162251</t>
+          <t>122454; 163953</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>215303; 267130</t>
+          <t>212273; 263087</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>205357; 254014</t>
+          <t>205186; 254108</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>135634; 183129</t>
+          <t>158294; 193583</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>340376; 399970</t>
+          <t>339442; 401310</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>480821; 552838</t>
+          <t>480637; 552469</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>472457; 544996</t>
+          <t>471895; 544464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>204890; 422474</t>
+          <t>339022; 399842</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173978</t>
+          <t>188232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>121680</t>
+          <t>134336</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>295657</t>
+          <t>322567</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>112451; 147281</t>
+          <t>109440; 145811</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>134040; 175997</t>
+          <t>135962; 178277</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125451; 168060</t>
+          <t>125185; 168245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153573; 195400</t>
+          <t>167490; 213175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35575; 62900</t>
+          <t>33863; 61300</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53366; 85060</t>
+          <t>53185; 85499</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95243; 133819</t>
+          <t>94486; 133653</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>107426; 137912</t>
+          <t>120569; 150700</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>152635; 199747</t>
+          <t>153555; 199264</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194661; 252713</t>
+          <t>195703; 251654</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>233352; 289122</t>
+          <t>231726; 291316</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>271396; 321799</t>
+          <t>296604; 354531</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68443</t>
+          <t>74883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>54563</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>117223</t>
+          <t>129446</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40946; 66732</t>
+          <t>41452; 65864</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39213; 68496</t>
+          <t>38541; 66479</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43907; 74340</t>
+          <t>44203; 72489</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56929; 81252</t>
+          <t>62556; 90127</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2833; 13351</t>
+          <t>2819; 13136</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11317; 30472</t>
+          <t>11356; 30601</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19593; 41574</t>
+          <t>20819; 41477</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20846; 79770</t>
+          <t>45229; 65897</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48053; 76143</t>
+          <t>47497; 76448</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54010; 90789</t>
+          <t>55994; 89249</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72234; 110461</t>
+          <t>72358; 110091</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>61668; 154196</t>
+          <t>114666; 147052</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>26972</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15410; 32477</t>
+          <t>14578; 31956</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17695; 38070</t>
+          <t>18278; 38607</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17042; 33185</t>
+          <t>16813; 33414</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13438; 26929</t>
+          <t>13411; 28250</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1115; 11607</t>
+          <t>1129; 11211</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1009; 12889</t>
+          <t>1006; 11906</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2768; 16517</t>
+          <t>2724; 17157</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3323; 10957</t>
+          <t>3619; 11527</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18099; 37871</t>
+          <t>18739; 39712</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21474; 44440</t>
+          <t>20546; 45497</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22306; 44679</t>
+          <t>22443; 45009</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18576; 34325</t>
+          <t>19504; 36843</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>901748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>651946</t>
+          <t>707214</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1486457</t>
+          <t>1608962</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1252736; 1365380</t>
+          <t>1249910; 1361442</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1203028; 1319774</t>
+          <t>1207570; 1324861</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1118666; 1233119</t>
+          <t>1127117; 1237940</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>659122; 919495</t>
+          <t>847849; 964672</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>781070; 876985</t>
+          <t>782094; 883362</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>905512; 1012153</t>
+          <t>901501; 1014393</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>869521; 974405</t>
+          <t>869748; 982473</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>541235; 718797</t>
+          <t>666059; 753555</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2058038; 2217789</t>
+          <t>2061715; 2208510</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2142650; 2302854</t>
+          <t>2140869; 2304193</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2015671; 2174376</t>
+          <t>2019716; 2177719</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1274431; 1605487</t>
+          <t>1528923; 1683254</t>
         </is>
       </c>
     </row>
